--- a/torch_to_mindspore_mapping.xlsx
+++ b/torch_to_mindspore_mapping.xlsx
@@ -14867,16 +14867,6 @@
       <c r="C842" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>mindspore.ops.flash_attention_score; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>参数和 layout 有差异; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
     </row>
     <row r="843" ht="16" customHeight="1">
       <c r="A843" s="1" t="inlineStr">
@@ -14917,18 +14907,7 @@
       <c r="C846" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D846" s="12" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.grouped_matmul; 
-mindspore.ops.auto_generate.grouped_matmul_v2; 
-mindspore.ops.auto_generate.grouped_matmul_v4; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E846" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；Ascend 融合算子，参数不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="D846" s="12" t="n"/>
     </row>
     <row r="847" ht="16" customHeight="1">
       <c r="A847" s="1" t="inlineStr">
@@ -15006,23 +14985,8 @@
           <t>torch_npu.npu_rms_norm</t>
         </is>
       </c>
-      <c r="B853" t="inlineStr">
-        <is>
-          <t>mindspore.ops.rms_norm</t>
-        </is>
-      </c>
       <c r="C853" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>hyper_parallel.models.modules.rmsnorm.RMSNorm</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>hyper-parallel 有 RMSNorm eager fallback/fused path 可参考</t>
-        </is>
       </c>
     </row>
     <row r="854" ht="16" customHeight="1">
@@ -15044,16 +15008,6 @@
       <c r="C855" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D855" t="inlineStr">
-        <is>
-          <t>mindspore.ops.rotary_position_embedding; hyper_parallel.models.modules.rope.apply_rotary_pos_emb; hyper_parallel.models.modules.rope.MultiModalRotaryEmbedding</t>
-        </is>
-      </c>
-      <c r="E855" t="inlineStr">
-        <is>
-          <t>rotary_mul 与 rotary_position_embedding 参数语义不同; hyper-parallel 有 RoPE/mRoPE 手写实现可参考，适合替代 rotary 类私有融合算子但需核对 shape/layout</t>
-        </is>
-      </c>
     </row>
     <row r="856" hidden="1" ht="16" customHeight="1">
       <c r="A856" s="1" t="inlineStr">
@@ -15061,23 +15015,8 @@
           <t>torch_npu.npu_swiglu</t>
         </is>
       </c>
-      <c r="B856" t="inlineStr">
-        <is>
-          <t>mindspore.ops.swiglu</t>
-        </is>
-      </c>
       <c r="C856" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E856" t="inlineStr">
-        <is>
-          <t>hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
       </c>
     </row>
     <row r="857" hidden="1" ht="16" customHeight="1">
@@ -15576,149 +15515,32 @@
       </c>
     </row>
     <row r="894" hidden="1" ht="16.8" customHeight="1">
-      <c r="A894" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="B894" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="C894" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D894" t="inlineStr">
-        <is>
-          <t>mindspore.ops.speed_fusion_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E894" t="inlineStr">
-        <is>
-          <t>推理融合注意力公开接口，参数和 layout 需核对; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A894" s="1" t="n"/>
+      <c r="C894" s="5" t="n"/>
     </row>
     <row r="895" hidden="1" ht="16.8" customHeight="1">
-      <c r="A895" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_grouped_matmul_finalize_routing</t>
-        </is>
-      </c>
-      <c r="C895" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D895" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.grouped_matmul; mindspore.ops.auto_generate.moe_finalize_routing; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E895" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；未找到单一对等接口，可拆分替代; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A895" s="1" t="n"/>
+      <c r="C895" s="5" t="n"/>
     </row>
     <row r="896" hidden="1" ht="16.8" customHeight="1">
-      <c r="A896" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_distribute_combine_v2</t>
-        </is>
-      </c>
-      <c r="C896" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D896" t="inlineStr">
-        <is>
-          <t>mindspore.ops.moe_distribute_combine; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E896" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；v2/参数可能不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A896" s="1" t="n"/>
+      <c r="C896" s="5" t="n"/>
     </row>
     <row r="897" hidden="1" ht="16.8" customHeight="1">
-      <c r="A897" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_distribute_dispatch_v2</t>
-        </is>
-      </c>
-      <c r="C897" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D897" t="inlineStr">
-        <is>
-          <t>mindspore.ops.moe_distribute_dispatch; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E897" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；v2/参数可能不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A897" s="1" t="n"/>
+      <c r="C897" s="5" t="n"/>
     </row>
     <row r="898" hidden="1" ht="16.8" customHeight="1">
-      <c r="A898" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_finalize_routing</t>
-        </is>
-      </c>
-      <c r="C898" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D898" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.moe_finalize_routing; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E898" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；参数不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A898" s="1" t="n"/>
+      <c r="C898" s="5" t="n"/>
     </row>
     <row r="899" hidden="1" ht="16.8" customHeight="1">
-      <c r="A899" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_gating_top_k</t>
-        </is>
-      </c>
-      <c r="C899" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.moe_gating_top_k_softmax; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E899" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；包含 softmax/top-k 语义，参数不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A899" s="1" t="n"/>
+      <c r="C899" s="5" t="n"/>
     </row>
     <row r="900" hidden="1" ht="16.8" customHeight="1">
-      <c r="A900" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_init_routing_v2</t>
-        </is>
-      </c>
-      <c r="C900" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t>mindspore.ops.moe_init_routing_v2; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E900" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；参数不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A900" s="1" t="n"/>
+      <c r="C900" s="5" t="n"/>
     </row>
     <row r="901" hidden="1" ht="16.8" customHeight="1">
       <c r="A901" s="1" t="inlineStr">
@@ -16481,24 +16303,8 @@
       </c>
     </row>
     <row r="949" hidden="1" ht="16.8" customHeight="1">
-      <c r="A949" s="1" t="inlineStr">
-        <is>
-          <t>torch.ops.custom.npu_ai_infra_kv_quant_sparse_flash_attention</t>
-        </is>
-      </c>
-      <c r="C949" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D949" t="inlineStr">
-        <is>
-          <t>mindspore.ops.sparse_flash_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E949" t="inlineStr">
-        <is>
-          <t>自定义接口，KV quant 参数需人工核对; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A949" s="1" t="n"/>
+      <c r="C949" s="5" t="n"/>
     </row>
     <row r="950" ht="16.8" customHeight="1">
       <c r="A950" s="1" t="inlineStr">
@@ -16521,24 +16327,8 @@
       </c>
     </row>
     <row r="952" hidden="1" ht="16.8" customHeight="1">
-      <c r="A952" s="1" t="inlineStr">
-        <is>
-          <t>torch.ops.custom.npu_ai_infra_sparse_flash_attention_pioneer</t>
-        </is>
-      </c>
-      <c r="C952" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D952" t="inlineStr">
-        <is>
-          <t>mindspore.ops.sparse_flash_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E952" t="inlineStr">
-        <is>
-          <t>自定义接口，参数需人工核对; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A952" s="1" t="n"/>
+      <c r="C952" s="5" t="n"/>
     </row>
     <row r="953" hidden="1" ht="16.8" customHeight="1">
       <c r="A953" s="1" t="inlineStr">
@@ -16581,29 +16371,8 @@
       </c>
     </row>
     <row r="955" hidden="1" ht="16.8" customHeight="1">
-      <c r="A955" s="1" t="inlineStr">
-        <is>
-          <t>torch.ops.npu.npu_fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="B955" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="C955" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D955" t="inlineStr">
-        <is>
-          <t>mindspore.ops.speed_fusion_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E955" t="inlineStr">
-        <is>
-          <t>参数和 layout 需核对; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A955" s="1" t="n"/>
+      <c r="C955" s="5" t="n"/>
     </row>
     <row r="956" ht="16.8" customHeight="1">
       <c r="A956" s="1" t="inlineStr">
@@ -16716,44 +16485,12 @@
       </c>
     </row>
     <row r="964" hidden="1" ht="16.8" customHeight="1">
-      <c r="A964" s="1" t="inlineStr">
-        <is>
-          <t>torch.ops.vllm.unified_attention</t>
-        </is>
-      </c>
-      <c r="C964" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D964" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score; mindspore.ops.flash_attention_score; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E964" t="inlineStr">
-        <is>
-          <t>vLLM 自定义接口，需按注意力场景改写; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A964" s="1" t="n"/>
+      <c r="C964" s="5" t="n"/>
     </row>
     <row r="965" hidden="1" ht="16.8" customHeight="1">
-      <c r="A965" s="1" t="inlineStr">
-        <is>
-          <t>torch.ops.vllm.unified_attention_with_output</t>
-        </is>
-      </c>
-      <c r="C965" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D965" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score; mindspore.ops.flash_attention_score; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E965" t="inlineStr">
-        <is>
-          <t>vLLM 自定义接口，需按注意力场景改写; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A965" s="1" t="n"/>
+      <c r="C965" s="5" t="n"/>
     </row>
     <row r="966" hidden="1" ht="16.8" customHeight="1">
       <c r="A966" s="1" t="inlineStr">
@@ -17326,49 +17063,12 @@
       </c>
     </row>
     <row r="1006" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1006" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_add_rms_norm</t>
-        </is>
-      </c>
-      <c r="B1006" t="inlineStr">
-        <is>
-          <t>mindspore.ops.add_rms_norm</t>
-        </is>
-      </c>
-      <c r="C1006" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1006" t="inlineStr">
-        <is>
-          <t>hyper_parallel.models.modules.rmsnorm.RMSNormGated</t>
-        </is>
-      </c>
-      <c r="E1006" t="inlineStr">
-        <is>
-          <t>hyper-parallel 有 gated RMSNorm 组合实现可参考，但不等价于 add_rms_norm 融合接口</t>
-        </is>
-      </c>
+      <c r="A1006" s="1" t="n"/>
+      <c r="C1006" s="5" t="n"/>
     </row>
     <row r="1007" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1007" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_apply_rotary_pos_emb</t>
-        </is>
-      </c>
-      <c r="C1007" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1007" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.apply_rotary_pos_emb; mindspore.ops.rotary_position_embedding; hyper_parallel.models.modules.rope.apply_rotary_pos_emb; hyper_parallel.models.modules.rope.MultiModalRotaryEmbedding</t>
-        </is>
-      </c>
-      <c r="E1007" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；参数语义需人工核对; hyper-parallel 有 RoPE/mRoPE 手写实现可参考，适合替代 rotary 类私有融合算子但需核对 shape/layout</t>
-        </is>
-      </c>
+      <c r="A1007" s="1" t="n"/>
+      <c r="C1007" s="5" t="n"/>
     </row>
     <row r="1008" ht="16.8" customHeight="1">
       <c r="A1008" s="1" t="inlineStr">
@@ -17421,99 +17121,20 @@
       </c>
     </row>
     <row r="1012" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1012" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_fused_infer_attention_score.out</t>
-        </is>
-      </c>
-      <c r="B1012" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="C1012" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1012" t="inlineStr">
-        <is>
-          <t>mindspore.ops.speed_fusion_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E1012" t="inlineStr">
-        <is>
-          <t>out 变体需改写为普通返回值; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A1012" s="1" t="n"/>
+      <c r="C1012" s="5" t="n"/>
     </row>
     <row r="1013" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1013" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_fused_infer_attention_score_v2</t>
-        </is>
-      </c>
-      <c r="B1013" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="C1013" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1013" t="inlineStr">
-        <is>
-          <t>mindspore.ops.speed_fusion_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E1013" t="inlineStr">
-        <is>
-          <t>v2 参数和 layout 需核对; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A1013" s="1" t="n"/>
+      <c r="C1013" s="5" t="n"/>
     </row>
     <row r="1014" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1014" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_fused_infer_attention_score_v2.out</t>
-        </is>
-      </c>
-      <c r="B1014" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="C1014" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1014" t="inlineStr">
-        <is>
-          <t>mindspore.ops.speed_fusion_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E1014" t="inlineStr">
-        <is>
-          <t>out/v2 变体需改写为普通返回值; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A1014" s="1" t="n"/>
+      <c r="C1014" s="5" t="n"/>
     </row>
     <row r="1015" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1015" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_interleave_rope</t>
-        </is>
-      </c>
-      <c r="C1015" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1015" t="inlineStr">
-        <is>
-          <t>mindspore.ops.rotary_position_embedding; hyper_parallel.models.modules.rope.apply_rotary_pos_emb; hyper_parallel.models.modules.rope.MultiModalRotaryEmbedding</t>
-        </is>
-      </c>
-      <c r="E1015" t="inlineStr">
-        <is>
-          <t>rotary/rope 类替代，参数不同; hyper-parallel 有 RoPE/mRoPE 手写实现可参考，适合替代 rotary 类私有融合算子但需核对 shape/layout</t>
-        </is>
-      </c>
+      <c r="A1015" s="1" t="n"/>
+      <c r="C1015" s="5" t="n"/>
     </row>
     <row r="1016" ht="16.8" customHeight="1">
       <c r="A1016" s="1" t="inlineStr">
@@ -17576,84 +17197,20 @@
       </c>
     </row>
     <row r="1022" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1022" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_compute_expert_tokens</t>
-        </is>
-      </c>
-      <c r="C1022" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1022" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.moe_compute_expert_tokens; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E1022" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；参数不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A1022" s="1" t="n"/>
+      <c r="C1022" s="5" t="n"/>
     </row>
     <row r="1023" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1023" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_gating_top_k_softmax</t>
-        </is>
-      </c>
-      <c r="C1023" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1023" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.moe_gating_top_k_softmax; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E1023" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；参数不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A1023" s="1" t="n"/>
+      <c r="C1023" s="5" t="n"/>
     </row>
     <row r="1024" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1024" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_moe_init_routing</t>
-        </is>
-      </c>
-      <c r="C1024" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1024" t="inlineStr">
-        <is>
-          <t>mindspore.ops.auto_generate.moe_init_routing; mindspore.ops.moe_init_routing_v2; hyper_parallel.platform.mindspore.multicore.moe_ffn_fwd/moe_ffn_bwd; hyper_parallel.platform.torch.common.moe.GroupedExperts</t>
-        </is>
-      </c>
-      <c r="E1024" t="inlineStr">
-        <is>
-          <t>代码已有，未对外；参数不同; hyper-parallel 有 MoE FFN/GroupedMatmul/SwiGLU 融合路径可参考，需按 omniinfer routing/tiling/workspace 参数人工适配</t>
-        </is>
-      </c>
+      <c r="A1024" s="1" t="n"/>
+      <c r="C1024" s="5" t="n"/>
     </row>
     <row r="1025" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1025" s="1" t="inlineStr">
-        <is>
-          <t>torch_npu.npu_mrope</t>
-        </is>
-      </c>
-      <c r="C1025" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1025" t="inlineStr">
-        <is>
-          <t>mindspore.ops.rotary_position_embedding; hyper_parallel.models.modules.rope.apply_rotary_pos_emb; hyper_parallel.models.modules.rope.MultiModalRotaryEmbedding</t>
-        </is>
-      </c>
-      <c r="E1025" t="inlineStr">
-        <is>
-          <t>mrope 需按多模态 rope 语义人工改写; hyper-parallel 有 RoPE/mRoPE 手写实现可参考，适合替代 rotary 类私有融合算子但需核对 shape/layout</t>
-        </is>
-      </c>
+      <c r="A1025" s="1" t="n"/>
+      <c r="C1025" s="5" t="n"/>
     </row>
     <row r="1026" ht="16.8" customHeight="1">
       <c r="A1026" s="1" t="inlineStr">
@@ -17776,29 +17333,8 @@
       </c>
     </row>
     <row r="1036" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1036" s="1" t="inlineStr">
-        <is>
-          <t>torchair.ops.npu_fused_infer_attention_score_v2</t>
-        </is>
-      </c>
-      <c r="B1036" t="inlineStr">
-        <is>
-          <t>mindspore.ops.fused_infer_attention_score</t>
-        </is>
-      </c>
-      <c r="C1036" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1036" t="inlineStr">
-        <is>
-          <t>mindspore.ops.speed_fusion_attention; hyper_parallel.core.shard.ops.parallel_npu_flash_attention_score.NPUFlashAttentionScoreDistributedOp</t>
-        </is>
-      </c>
-      <c r="E1036" t="inlineStr">
-        <is>
-          <t>torchair 编译后端接口，迁移时改用 MindSpore 原生接口; hyper-parallel 可参考分布式 npu_fusion_attention 封装和 layout/sharding 测试，不是直接 MindSpore 公共 API</t>
-        </is>
-      </c>
+      <c r="A1036" s="1" t="n"/>
+      <c r="C1036" s="5" t="n"/>
     </row>
     <row r="1037" ht="16.8" customHeight="1">
       <c r="A1037" s="1" t="inlineStr">

--- a/torch_to_mindspore_mapping.xlsx
+++ b/torch_to_mindspore_mapping.xlsx
@@ -1934,13 +1934,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>mindspore.device_context.cpu/gpu/ascend.device_count</t>
+          <t>mindspore.device_context.gpu.device_count</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="4" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>mindspore.device_context.cpu.device_count; mindspore.device_context.ascend.device_count</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>原写法 mindspore.device_context.cpu/gpu/ascend.device_count 不是有效 API；CUDA 场景优先对应 GPU</t>
+        </is>
+      </c>
     </row>
     <row r="49" hidden="1" ht="16" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
@@ -1990,14 +1999,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>mindspore.device_context.cpu/gpu/ascend.is_available</t>
+          <t>mindspore.device_context.gpu.is_available</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="9" t="n"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>mindspore.device_context.cpu.is_available; mindspore.device_context.ascend.is_available</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>原写法 mindspore.device_context.cpu/gpu/ascend.is_available 不是有效 API；CUDA 场景优先对应 GPU</t>
+        </is>
+      </c>
     </row>
     <row r="52" hidden="1" ht="16" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -3266,15 +3283,20 @@
           <t>torch.is_tensor</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>mindspore.is_tensor</t>
-        </is>
-      </c>
+      <c r="B121" s="4" t="n"/>
       <c r="C121" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D121" s="4" t="n"/>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>isinstance(obj, mindspore.Tensor)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>mindspore.is_tensor 已废弃，2.9.0 后将删除</t>
+        </is>
+      </c>
     </row>
     <row r="122" hidden="1" ht="16" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
@@ -4293,7 +4315,7 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>mindspore.nn.DropOut3d</t>
+          <t>mindspore.nn.Dropout3d</t>
         </is>
       </c>
       <c r="C178" s="5" t="n">
@@ -5457,7 +5479,7 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>mindspore.parallel.distributedDistributedDataParallel</t>
+          <t>mindspore.parallel.distributed.DistributedDataParallel</t>
         </is>
       </c>
       <c r="C243" s="5" t="n">
@@ -5869,17 +5891,18 @@
           <t>torch.no_grad</t>
         </is>
       </c>
-      <c r="B267" s="8" t="inlineStr">
+      <c r="B267" s="8" t="n"/>
+      <c r="C267" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" t="inlineStr">
         <is>
           <t>mindspore._no_grad</t>
         </is>
       </c>
-      <c r="C267" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E267" s="6" t="inlineStr">
         <is>
-          <t>参考：https://www.hiascend.com/forum/thread-0289146760766805055-1-1.html</t>
+          <t>代码已有，未对外；参考：https://www.hiascend.com/forum/thread-0289146760766805055-1-1.html</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8264,16 @@
       <c r="C408" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D408" s="4" t="n"/>
+      <c r="D408" s="4" t="inlineStr">
+        <is>
+          <t>mindspore.mint.where</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>最新文档提示 2.9.0 后 masked_fill_ 返回值将改为无显式返回；可按场景改写为 where</t>
+        </is>
+      </c>
     </row>
     <row r="409" hidden="1" ht="16" customHeight="1">
       <c r="A409" s="4" t="inlineStr">
@@ -9958,18 +9990,18 @@
           <t>torch_scatter.scatter_max</t>
         </is>
       </c>
-      <c r="B512" s="4" t="inlineStr">
+      <c r="B512" s="4" t="n"/>
+      <c r="C512" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D512" s="4" t="inlineStr">
         <is>
           <t>mindspore.ops.scatter_max</t>
         </is>
       </c>
-      <c r="C512" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D512" s="4" t="n"/>
       <c r="E512" s="8" t="inlineStr">
         <is>
-          <t>torch_scatter：https://pytorch-scatter.readthedocs.io/en/1.3.0/functions/max.html</t>
+          <t>torch_scatter：https://pytorch-scatter.readthedocs.io/en/1.3.0/functions/max.html；mindspore.ops.scatter_max 已废弃，2.9.0 后将删除，未找到公开非废弃对等接口</t>
         </is>
       </c>
     </row>
@@ -10525,13 +10557,17 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.current_stream</t>
+          <t>mindspore.runtime.current_stream</t>
         </is>
       </c>
       <c r="C549" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E549" s="2" t="n"/>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="550" hidden="1" ht="16" customHeight="1">
       <c r="A550" s="1" t="inlineStr">
@@ -10541,13 +10577,17 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.default_stream</t>
+          <t>mindspore.runtime.default_stream</t>
         </is>
       </c>
       <c r="C550" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E550" s="2" t="n"/>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="551" hidden="1" ht="16" customHeight="1">
       <c r="A551" s="1" t="inlineStr">
@@ -10652,13 +10692,17 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.max_memory_allocated</t>
+          <t>mindspore.runtime.max_memory_allocated</t>
         </is>
       </c>
       <c r="C556" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E556" s="2" t="n"/>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="557" hidden="1" ht="16" customHeight="1">
       <c r="A557" s="1" t="inlineStr">
@@ -10668,13 +10712,17 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.max_memory_reserved</t>
+          <t>mindspore.runtime.max_memory_reserved</t>
         </is>
       </c>
       <c r="C557" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E557" s="2" t="n"/>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="558" hidden="1" ht="16" customHeight="1">
       <c r="A558" s="1" t="inlineStr">
@@ -10684,13 +10732,17 @@
       </c>
       <c r="B558" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.memory_allocated</t>
+          <t>mindspore.runtime.memory_allocated</t>
         </is>
       </c>
       <c r="C558" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E558" s="2" t="n"/>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="559" hidden="1" ht="16" customHeight="1">
       <c r="A559" s="1" t="inlineStr">
@@ -10700,13 +10752,17 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.memory_reserved</t>
+          <t>mindspore.runtime.memory_reserved</t>
         </is>
       </c>
       <c r="C559" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E559" s="2" t="n"/>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="560" hidden="1" ht="16" customHeight="1">
       <c r="A560" s="1" t="inlineStr">
@@ -10716,13 +10772,17 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.memory_stats</t>
+          <t>mindspore.runtime.memory_stats</t>
         </is>
       </c>
       <c r="C560" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E560" s="2" t="n"/>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="561" hidden="1" ht="16" customHeight="1">
       <c r="A561" s="1" t="inlineStr">
@@ -10748,13 +10808,17 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.Stream</t>
+          <t>mindspore.runtime.Stream</t>
         </is>
       </c>
       <c r="C562" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E562" s="2" t="n"/>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="563" hidden="1" ht="16" customHeight="1">
       <c r="A563" s="1" t="inlineStr">
@@ -11469,13 +11533,17 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.current_stream</t>
+          <t>mindspore.runtime.current_stream</t>
         </is>
       </c>
       <c r="C605" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E605" s="2" t="n"/>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="606" hidden="1" ht="16" customHeight="1">
       <c r="A606" s="1" t="inlineStr">
@@ -11485,13 +11553,17 @@
       </c>
       <c r="B606" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.default_stream</t>
+          <t>mindspore.runtime.default_stream</t>
         </is>
       </c>
       <c r="C606" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E606" s="2" t="n"/>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="607" hidden="1" ht="16" customHeight="1">
       <c r="A607" s="1" t="inlineStr">
@@ -11501,13 +11573,22 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.device_count</t>
+          <t>mindspore.device_context.ascend.device_count</t>
         </is>
       </c>
       <c r="C607" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E607" s="2" t="n"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>mindspore.device_context.cpu.device_count; mindspore.device_context.gpu.device_count</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>mindspore.hal.device_count 已废弃；NPU 场景优先对应 ascend</t>
+        </is>
+      </c>
     </row>
     <row r="608" hidden="1" ht="16" customHeight="1">
       <c r="A608" s="1" t="inlineStr">
@@ -11517,13 +11598,17 @@
       </c>
       <c r="B608" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.empty_cache</t>
+          <t>mindspore.runtime.empty_cache</t>
         </is>
       </c>
       <c r="C608" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E608" s="2" t="n"/>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="609" hidden="1" ht="16" customHeight="1">
       <c r="A609" s="1" t="inlineStr">
@@ -11533,13 +11618,17 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.Event</t>
+          <t>mindspore.runtime.Event</t>
         </is>
       </c>
       <c r="C609" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E609" s="2" t="n"/>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="610" hidden="1" ht="16" customHeight="1">
       <c r="A610" s="1" t="inlineStr">
@@ -11549,13 +11638,22 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.is_available</t>
+          <t>mindspore.device_context.ascend.is_available</t>
         </is>
       </c>
       <c r="C610" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E610" s="2" t="n"/>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>mindspore.device_context.cpu.is_available; mindspore.device_context.gpu.is_available</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>mindspore.hal.is_available 已废弃；NPU 场景优先对应 ascend</t>
+        </is>
+      </c>
     </row>
     <row r="611" hidden="1" ht="16" customHeight="1">
       <c r="A611" s="1" t="inlineStr">
@@ -11565,13 +11663,17 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.max_memory_allocated</t>
+          <t>mindspore.runtime.max_memory_allocated</t>
         </is>
       </c>
       <c r="C611" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E611" s="2" t="n"/>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="612" hidden="1" ht="16" customHeight="1">
       <c r="A612" s="1" t="inlineStr">
@@ -11581,13 +11683,17 @@
       </c>
       <c r="B612" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.max_memory_reserved</t>
+          <t>mindspore.runtime.max_memory_reserved</t>
         </is>
       </c>
       <c r="C612" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E612" s="2" t="n"/>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="613" hidden="1" ht="16" customHeight="1">
       <c r="A613" s="1" t="inlineStr">
@@ -11597,13 +11703,17 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.memory_allocated</t>
+          <t>mindspore.runtime.memory_allocated</t>
         </is>
       </c>
       <c r="C613" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E613" s="2" t="n"/>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="614" hidden="1" ht="16" customHeight="1">
       <c r="A614" s="1" t="inlineStr">
@@ -11613,13 +11723,17 @@
       </c>
       <c r="B614" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.memory_reserved</t>
+          <t>mindspore.runtime.memory_reserved</t>
         </is>
       </c>
       <c r="C614" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E614" s="2" t="n"/>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="615" hidden="1" ht="16" customHeight="1">
       <c r="A615" s="1" t="inlineStr">
@@ -11629,13 +11743,17 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.memory_stats</t>
+          <t>mindspore.runtime.memory_stats</t>
         </is>
       </c>
       <c r="C615" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E615" s="2" t="n"/>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="616" hidden="1" ht="16" customHeight="1">
       <c r="A616" s="1" t="inlineStr">
@@ -11645,13 +11763,17 @@
       </c>
       <c r="B616" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.reset_peak_memory_stats</t>
+          <t>mindspore.runtime.reset_peak_memory_stats</t>
         </is>
       </c>
       <c r="C616" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E616" s="2" t="n"/>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="617" hidden="1" ht="16" customHeight="1">
       <c r="A617" s="1" t="inlineStr">
@@ -11677,13 +11799,17 @@
       </c>
       <c r="B618" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.Stream</t>
+          <t>mindspore.runtime.Stream</t>
         </is>
       </c>
       <c r="C618" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E618" s="2" t="n"/>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="619" hidden="1" ht="16" customHeight="1">
       <c r="A619" s="1" t="inlineStr">
@@ -11693,13 +11819,17 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.synchronize</t>
+          <t>mindspore.runtime.synchronize</t>
         </is>
       </c>
       <c r="C619" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E619" s="2" t="n"/>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="620" hidden="1" ht="16" customHeight="1">
       <c r="A620" s="1" t="inlineStr">
@@ -12567,13 +12697,17 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.current_stream</t>
+          <t>mindspore.runtime.current_stream</t>
         </is>
       </c>
       <c r="C672" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E672" s="2" t="n"/>
+      <c r="E672" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="673" hidden="1" ht="16" customHeight="1">
       <c r="A673" s="1" t="inlineStr">
@@ -12583,13 +12717,17 @@
       </c>
       <c r="B673" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.empty_cache</t>
+          <t>mindspore.runtime.empty_cache</t>
         </is>
       </c>
       <c r="C673" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E673" s="2" t="n"/>
+      <c r="E673" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="674" hidden="1" ht="16" customHeight="1">
       <c r="A674" s="1" t="inlineStr">
@@ -12599,13 +12737,17 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.Event</t>
+          <t>mindspore.runtime.Event</t>
         </is>
       </c>
       <c r="C674" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E674" s="2" t="n"/>
+      <c r="E674" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="675" hidden="1" ht="16" customHeight="1">
       <c r="A675" s="1" t="inlineStr">
@@ -12613,15 +12755,20 @@
           <t>torch_npu.npu.get_device_name</t>
         </is>
       </c>
-      <c r="B675" s="1" t="inlineStr">
+      <c r="B675" s="1" t="n"/>
+      <c r="C675" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D675" t="inlineStr">
         <is>
           <t>mindspore.hal.get_device_name</t>
         </is>
       </c>
-      <c r="C675" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E675" s="2" t="n"/>
+      <c r="E675" s="2" t="inlineStr">
+        <is>
+          <t>MindSpore 文档说明 hal.get_device_name 后续将废弃，未找到 runtime/device_context 公开对等接口</t>
+        </is>
+      </c>
     </row>
     <row r="676" hidden="1" ht="16" customHeight="1">
       <c r="A676" s="1" t="inlineStr">
@@ -12663,13 +12810,17 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>mindspore.set_context</t>
+          <t>mindspore.device_context.ascend.op_tuning.op_compile</t>
         </is>
       </c>
       <c r="C678" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E678" s="2" t="n"/>
+      <c r="E678" s="2" t="inlineStr">
+        <is>
+          <t>set_context(ascend_config={"jit_compile": ...}) 已废弃，最新文档建议使用 ascend.op_tuning.op_compile；需核对 torch_npu set_compile_mode 语义</t>
+        </is>
+      </c>
     </row>
     <row r="679" hidden="1" ht="16" customHeight="1">
       <c r="A679" s="1" t="inlineStr">
@@ -12679,13 +12830,17 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>mindspore.hal.StreamCtx</t>
+          <t>mindspore.runtime.StreamCtx</t>
         </is>
       </c>
       <c r="C679" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E679" s="2" t="n"/>
+      <c r="E679" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="680" hidden="1" ht="16" customHeight="1">
       <c r="A680" s="1" t="inlineStr">
@@ -12695,13 +12850,17 @@
       </c>
       <c r="B680" s="1" t="inlineStr">
         <is>
-          <t>mindspore.hal.synchronize</t>
+          <t>mindspore.runtime.synchronize</t>
         </is>
       </c>
       <c r="C680" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E680" s="2" t="n"/>
+      <c r="E680" s="2" t="inlineStr">
+        <is>
+          <t>hal 接口已废弃，按最新 MindSpore 文档改用 runtime</t>
+        </is>
+      </c>
     </row>
     <row r="681" hidden="1" ht="16" customHeight="1">
       <c r="A681" s="1" t="inlineStr">
@@ -13839,12 +13998,12 @@
       </c>
       <c r="D753" s="2" t="inlineStr">
         <is>
-          <t>hyper_parallel.fully_shard; hyper_parallel.HSDPModule; mindspore.parallel.auto_parallel.AutoParallel.hsdp; mindspore.set_auto_parallel_context(enable_parallel_optimizer=True); mindspore.parallel.distributed.DistributedDataParallel</t>
+          <t>hyper_parallel.fully_shard; hyper_parallel.HSDPModule; mindspore.parallel.auto_parallel.AutoParallel.hsdp; mindspore.parallel.distributed.DistributedDataParallel</t>
         </is>
       </c>
       <c r="E753" s="2" t="inlineStr">
         <is>
-          <t>HyperParallel HSDP是最接近FSDP的外部库替代；MindSpore原生可用自动/半自动并行、优化器并行或DDP，但不是同名等价封装</t>
+          <t>HyperParallel HSDP是最接近FSDP的外部库替代；MindSpore原生可用 AutoParallel/HSDP 或 DDP，但不是同名等价封装；已移除废弃的 set_auto_parallel_context 建议</t>
         </is>
       </c>
     </row>
@@ -14867,6 +15026,16 @@
       <c r="C842" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>mindspore.ops.flash_attention_score</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>参数和 layout 有差异</t>
+        </is>
+      </c>
     </row>
     <row r="843" ht="16" customHeight="1">
       <c r="A843" s="1" t="inlineStr">
@@ -14907,7 +15076,16 @@
       <c r="C846" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D846" s="12" t="n"/>
+      <c r="D846" s="12" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.grouped_matmul; mindspore.ops.auto_generate.grouped_matmul_v2; mindspore.ops.auto_generate.grouped_matmul_v4</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；Ascend 融合算子，参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="847" ht="16" customHeight="1">
       <c r="A847" s="1" t="inlineStr">
@@ -14985,6 +15163,11 @@
           <t>torch_npu.npu_rms_norm</t>
         </is>
       </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>mindspore.ops.rms_norm</t>
+        </is>
+      </c>
       <c r="C853" s="5" t="n">
         <v>1</v>
       </c>
@@ -15008,6 +15191,16 @@
       <c r="C855" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>mindspore.ops.rotary_position_embedding</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>rotary_mul 与 rotary_position_embedding 参数语义不同</t>
+        </is>
+      </c>
     </row>
     <row r="856" hidden="1" ht="16" customHeight="1">
       <c r="A856" s="1" t="inlineStr">
@@ -15015,6 +15208,11 @@
           <t>torch_npu.npu_swiglu</t>
         </is>
       </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>mindspore.ops.swiglu</t>
+        </is>
+      </c>
       <c r="C856" s="5" t="n">
         <v>1</v>
       </c>
@@ -15415,17 +15613,17 @@
           <t>torch.npu.get_device_name</t>
         </is>
       </c>
-      <c r="B889" t="inlineStr">
+      <c r="C889" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D889" t="inlineStr">
         <is>
           <t>mindspore.hal.get_device_name</t>
         </is>
       </c>
-      <c r="C889" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>MindSpore 文档说明该接口后续将废弃</t>
+          <t>MindSpore 文档说明 hal.get_device_name 后续将废弃，未找到 runtime/device_context 公开对等接口</t>
         </is>
       </c>
     </row>
@@ -15515,32 +15713,149 @@
       </c>
     </row>
     <row r="894" hidden="1" ht="16.8" customHeight="1">
-      <c r="A894" s="1" t="n"/>
-      <c r="C894" s="5" t="n"/>
+      <c r="A894" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="C894" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>mindspore.ops.speed_fusion_attention</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>推理融合注意力公开接口，参数和 layout 需核对</t>
+        </is>
+      </c>
     </row>
     <row r="895" hidden="1" ht="16.8" customHeight="1">
-      <c r="A895" s="1" t="n"/>
-      <c r="C895" s="5" t="n"/>
+      <c r="A895" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_grouped_matmul_finalize_routing</t>
+        </is>
+      </c>
+      <c r="C895" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.grouped_matmul; mindspore.ops.auto_generate.moe_finalize_routing</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；未找到单一对等接口，可拆分替代</t>
+        </is>
+      </c>
     </row>
     <row r="896" hidden="1" ht="16.8" customHeight="1">
-      <c r="A896" s="1" t="n"/>
-      <c r="C896" s="5" t="n"/>
+      <c r="A896" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_distribute_combine_v2</t>
+        </is>
+      </c>
+      <c r="C896" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>mindspore.ops.moe_distribute_combine</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；v2/参数可能不同</t>
+        </is>
+      </c>
     </row>
     <row r="897" hidden="1" ht="16.8" customHeight="1">
-      <c r="A897" s="1" t="n"/>
-      <c r="C897" s="5" t="n"/>
+      <c r="A897" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_distribute_dispatch_v2</t>
+        </is>
+      </c>
+      <c r="C897" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>mindspore.ops.moe_distribute_dispatch</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；v2/参数可能不同</t>
+        </is>
+      </c>
     </row>
     <row r="898" hidden="1" ht="16.8" customHeight="1">
-      <c r="A898" s="1" t="n"/>
-      <c r="C898" s="5" t="n"/>
+      <c r="A898" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_finalize_routing</t>
+        </is>
+      </c>
+      <c r="C898" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.moe_finalize_routing</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="899" hidden="1" ht="16.8" customHeight="1">
-      <c r="A899" s="1" t="n"/>
-      <c r="C899" s="5" t="n"/>
+      <c r="A899" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_gating_top_k</t>
+        </is>
+      </c>
+      <c r="C899" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.moe_gating_top_k_softmax</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；包含 softmax/top-k 语义，参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="900" hidden="1" ht="16.8" customHeight="1">
-      <c r="A900" s="1" t="n"/>
-      <c r="C900" s="5" t="n"/>
+      <c r="A900" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_init_routing_v2</t>
+        </is>
+      </c>
+      <c r="C900" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>mindspore.ops.moe_init_routing_v2</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="901" hidden="1" ht="16.8" customHeight="1">
       <c r="A901" s="1" t="inlineStr">
@@ -15683,12 +15998,12 @@
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>mindspore.hal; mindspore.set_device</t>
+          <t>mindspore.runtime; mindspore.set_device; mindspore.device_context.gpu</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>设备运行时模块替代，非一对一等价</t>
+          <t>设备运行时模块替代，非一对一等价；已移除废弃 hal 模块</t>
         </is>
       </c>
     </row>
@@ -15753,12 +16068,12 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>mindspore.get_context("device_target")</t>
+          <t>mindspore.get_current_device</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>只能获取 device_target，不是 torch device 对象</t>
+          <t>只能获取当前 MindSpore 设备信息，不是 torch device 对象；原 mindspore.get_context("device_target") 已废弃</t>
         </is>
       </c>
     </row>
@@ -15840,7 +16155,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>mindspore.ops.masked_fill</t>
+          <t>mindspore.mint.where</t>
         </is>
       </c>
       <c r="C919" s="5" t="n">
@@ -15849,6 +16164,11 @@
       <c r="D919" t="inlineStr">
         <is>
           <t>mindspore.Tensor.masked_fill</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>mindspore.ops.masked_fill 已废弃，建议改写为 where(mask, value, input)，需处理 value 广播/类型</t>
         </is>
       </c>
     </row>
@@ -15953,12 +16273,12 @@
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>mindspore.hal; mindspore.set_device</t>
+          <t>mindspore.runtime; mindspore.set_device; mindspore.device_context.ascend</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>NPU 运行时模块替代，非一对一等价</t>
+          <t>NPU 运行时模块替代，非一对一等价；已移除废弃 hal 模块</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16348,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>仅能替代部分设备属性</t>
+          <t>仅能替代部分设备属性；hal 设备属性查询接口后续将废弃，未找到 runtime/device_context 公开对等接口</t>
         </is>
       </c>
     </row>
@@ -16138,13 +16458,18 @@
           <t>torch.npu.mem_get_info</t>
         </is>
       </c>
-      <c r="B936" t="inlineStr">
-        <is>
-          <t>mindspore.hal.mem_get_info</t>
-        </is>
-      </c>
       <c r="C936" s="5" t="n">
         <v>1</v>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>mindspore.runtime.memory_stats; mindspore.runtime.memory_reserved; mindspore.runtime.memory_allocated</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>最新代码/docs 未找到 mindspore.hal.mem_get_info；可用 memory_* 组合近似，非一对一等价</t>
+        </is>
       </c>
     </row>
     <row r="937" hidden="1" ht="16.8" customHeight="1">
@@ -16158,12 +16483,12 @@
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>mindspore.runtime.memory; mindspore.hal</t>
+          <t>mindspore.runtime.memory_stats; mindspore.runtime.memory_reserved; mindspore.runtime.memory_allocated; mindspore.runtime.empty_cache</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>运行时内存模块替代，非一对一等价</t>
+          <t>运行时内存接口替代，非一对一等价；已移除废弃 hal 模块</t>
         </is>
       </c>
     </row>
@@ -16303,8 +16628,24 @@
       </c>
     </row>
     <row r="949" hidden="1" ht="16.8" customHeight="1">
-      <c r="A949" s="1" t="n"/>
-      <c r="C949" s="5" t="n"/>
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>torch.ops.custom.npu_ai_infra_kv_quant_sparse_flash_attention</t>
+        </is>
+      </c>
+      <c r="C949" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>mindspore.ops.sparse_flash_attention</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>自定义接口，KV quant 参数需人工核对</t>
+        </is>
+      </c>
     </row>
     <row r="950" ht="16.8" customHeight="1">
       <c r="A950" s="1" t="inlineStr">
@@ -16327,8 +16668,24 @@
       </c>
     </row>
     <row r="952" hidden="1" ht="16.8" customHeight="1">
-      <c r="A952" s="1" t="n"/>
-      <c r="C952" s="5" t="n"/>
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>torch.ops.custom.npu_ai_infra_sparse_flash_attention_pioneer</t>
+        </is>
+      </c>
+      <c r="C952" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>mindspore.ops.sparse_flash_attention</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>自定义接口，参数需人工核对</t>
+        </is>
+      </c>
     </row>
     <row r="953" hidden="1" ht="16.8" customHeight="1">
       <c r="A953" s="1" t="inlineStr">
@@ -16371,8 +16728,29 @@
       </c>
     </row>
     <row r="955" hidden="1" ht="16.8" customHeight="1">
-      <c r="A955" s="1" t="n"/>
-      <c r="C955" s="5" t="n"/>
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>torch.ops.npu.npu_fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="C955" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>mindspore.ops.speed_fusion_attention</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>参数和 layout 需核对</t>
+        </is>
+      </c>
     </row>
     <row r="956" ht="16.8" customHeight="1">
       <c r="A956" s="1" t="inlineStr">
@@ -16485,12 +16863,44 @@
       </c>
     </row>
     <row r="964" hidden="1" ht="16.8" customHeight="1">
-      <c r="A964" s="1" t="n"/>
-      <c r="C964" s="5" t="n"/>
+      <c r="A964" s="1" t="inlineStr">
+        <is>
+          <t>torch.ops.vllm.unified_attention</t>
+        </is>
+      </c>
+      <c r="C964" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score; mindspore.ops.flash_attention_score</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>vLLM 自定义接口，需按注意力场景改写</t>
+        </is>
+      </c>
     </row>
     <row r="965" hidden="1" ht="16.8" customHeight="1">
-      <c r="A965" s="1" t="n"/>
-      <c r="C965" s="5" t="n"/>
+      <c r="A965" s="1" t="inlineStr">
+        <is>
+          <t>torch.ops.vllm.unified_attention_with_output</t>
+        </is>
+      </c>
+      <c r="C965" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score; mindspore.ops.flash_attention_score</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>vLLM 自定义接口，需按注意力场景改写</t>
+        </is>
+      </c>
     </row>
     <row r="966" hidden="1" ht="16.8" customHeight="1">
       <c r="A966" s="1" t="inlineStr">
@@ -17063,12 +17473,39 @@
       </c>
     </row>
     <row r="1006" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1006" s="1" t="n"/>
-      <c r="C1006" s="5" t="n"/>
+      <c r="A1006" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_add_rms_norm</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>mindspore.ops.add_rms_norm</t>
+        </is>
+      </c>
+      <c r="C1006" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1007" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1007" s="1" t="n"/>
-      <c r="C1007" s="5" t="n"/>
+      <c r="A1007" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_apply_rotary_pos_emb</t>
+        </is>
+      </c>
+      <c r="C1007" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.apply_rotary_pos_emb; mindspore.ops.rotary_position_embedding</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；参数语义需人工核对</t>
+        </is>
+      </c>
     </row>
     <row r="1008" ht="16.8" customHeight="1">
       <c r="A1008" s="1" t="inlineStr">
@@ -17121,20 +17558,99 @@
       </c>
     </row>
     <row r="1012" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1012" s="1" t="n"/>
-      <c r="C1012" s="5" t="n"/>
+      <c r="A1012" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_fused_infer_attention_score.out</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="C1012" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>mindspore.ops.speed_fusion_attention</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>out 变体需改写为普通返回值</t>
+        </is>
+      </c>
     </row>
     <row r="1013" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1013" s="1" t="n"/>
-      <c r="C1013" s="5" t="n"/>
+      <c r="A1013" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_fused_infer_attention_score_v2</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="C1013" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>mindspore.ops.speed_fusion_attention</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>v2 参数和 layout 需核对</t>
+        </is>
+      </c>
     </row>
     <row r="1014" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1014" s="1" t="n"/>
-      <c r="C1014" s="5" t="n"/>
+      <c r="A1014" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_fused_infer_attention_score_v2.out</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="C1014" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>mindspore.ops.speed_fusion_attention</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>out/v2 变体需改写为普通返回值</t>
+        </is>
+      </c>
     </row>
     <row r="1015" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1015" s="1" t="n"/>
-      <c r="C1015" s="5" t="n"/>
+      <c r="A1015" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_interleave_rope</t>
+        </is>
+      </c>
+      <c r="C1015" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>mindspore.ops.rotary_position_embedding</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>rotary/rope 类替代，参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="1016" ht="16.8" customHeight="1">
       <c r="A1016" s="1" t="inlineStr">
@@ -17197,20 +17713,84 @@
       </c>
     </row>
     <row r="1022" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1022" s="1" t="n"/>
-      <c r="C1022" s="5" t="n"/>
+      <c r="A1022" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_compute_expert_tokens</t>
+        </is>
+      </c>
+      <c r="C1022" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.moe_compute_expert_tokens</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="1023" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1023" s="1" t="n"/>
-      <c r="C1023" s="5" t="n"/>
+      <c r="A1023" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_gating_top_k_softmax</t>
+        </is>
+      </c>
+      <c r="C1023" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.moe_gating_top_k_softmax</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="1024" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1024" s="1" t="n"/>
-      <c r="C1024" s="5" t="n"/>
+      <c r="A1024" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_moe_init_routing</t>
+        </is>
+      </c>
+      <c r="C1024" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>mindspore.ops.auto_generate.moe_init_routing; mindspore.ops.moe_init_routing_v2</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>代码已有，未对外；参数不同</t>
+        </is>
+      </c>
     </row>
     <row r="1025" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1025" s="1" t="n"/>
-      <c r="C1025" s="5" t="n"/>
+      <c r="A1025" s="1" t="inlineStr">
+        <is>
+          <t>torch_npu.npu_mrope</t>
+        </is>
+      </c>
+      <c r="C1025" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>mindspore.ops.rotary_position_embedding</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>mrope 需按多模态 rope 语义人工改写</t>
+        </is>
+      </c>
     </row>
     <row r="1026" ht="16.8" customHeight="1">
       <c r="A1026" s="1" t="inlineStr">
@@ -17333,8 +17913,29 @@
       </c>
     </row>
     <row r="1036" hidden="1" ht="16.8" customHeight="1">
-      <c r="A1036" s="1" t="n"/>
-      <c r="C1036" s="5" t="n"/>
+      <c r="A1036" s="1" t="inlineStr">
+        <is>
+          <t>torchair.ops.npu_fused_infer_attention_score_v2</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>mindspore.ops.fused_infer_attention_score</t>
+        </is>
+      </c>
+      <c r="C1036" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>mindspore.ops.speed_fusion_attention</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>torchair 编译后端接口，迁移时改用 MindSpore 原生接口</t>
+        </is>
+      </c>
     </row>
     <row r="1037" ht="16.8" customHeight="1">
       <c r="A1037" s="1" t="inlineStr">

--- a/torch_to_mindspore_mapping.xlsx
+++ b/torch_to_mindspore_mapping.xlsx
@@ -5358,7 +5358,7 @@
     <t>mindspore.multiprocessing.get_context</t>
   </si>
   <si>
-    <t>张浩：底层 Tensor 序列化/共享能力不完全等同于 pytorch</t>
+    <t>蔡福壁：理论上功能一致</t>
   </si>
   <si>
     <t>torch.multiprocessing.Queue</t>
@@ -19002,11 +19002,11 @@
       <c r="A910" s="2" t="s">
         <v>1762</v>
       </c>
+      <c r="B910" t="s">
+        <v>1763</v>
+      </c>
       <c r="C910" s="5">
         <v>1</v>
-      </c>
-      <c r="D910" t="s">
-        <v>1763</v>
       </c>
       <c r="E910" s="13" t="s">
         <v>1764</v>
@@ -19016,11 +19016,11 @@
       <c r="A911" s="2" t="s">
         <v>1765</v>
       </c>
+      <c r="B911" t="s">
+        <v>1766</v>
+      </c>
       <c r="C911" s="5">
         <v>1</v>
-      </c>
-      <c r="D911" t="s">
-        <v>1766</v>
       </c>
       <c r="E911" s="13" t="s">
         <v>1764</v>

--- a/torch_to_mindspore_mapping.xlsx
+++ b/torch_to_mindspore_mapping.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="1984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2203" uniqueCount="1983">
   <si>
     <t>Torch_API</t>
   </si>
@@ -5152,9 +5152,6 @@
   </si>
   <si>
     <t>torch.get_default_dtype</t>
-  </si>
-  <si>
-    <t>mindspore.get_context("device_id")</t>
   </si>
   <si>
     <t>torch.narrow</t>
@@ -8041,9 +8038,7 @@
       <c r="C72" s="5">
         <v>1</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>148</v>
-      </c>
+      <c r="D72" s="4"/>
       <c r="E72" s="2"/>
     </row>
     <row r="73" s="1" customFormat="1" ht="31" customHeight="1" spans="1:5">
@@ -18566,32 +18561,30 @@
       <c r="C877" s="5">
         <v>1</v>
       </c>
-      <c r="D877" s="7" t="s">
-        <v>1697</v>
-      </c>
+      <c r="D877" s="7"/>
       <c r="E877" s="2"/>
     </row>
     <row r="878" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A878" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B878" t="s">
         <v>1698</v>
       </c>
-      <c r="B878" t="s">
+      <c r="C878" s="5">
+        <v>1</v>
+      </c>
+      <c r="D878" t="s">
         <v>1699</v>
-      </c>
-      <c r="C878" s="5">
-        <v>1</v>
-      </c>
-      <c r="D878" t="s">
-        <v>1700</v>
       </c>
       <c r="E878" s="2"/>
     </row>
     <row r="879" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:3">
       <c r="A879" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B879" s="2" t="s">
         <v>1701</v>
-      </c>
-      <c r="B879" s="2" t="s">
-        <v>1702</v>
       </c>
       <c r="C879" s="5">
         <v>1</v>
@@ -18599,7 +18592,7 @@
     </row>
     <row r="880" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A880" s="2" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="B880" t="s">
         <v>1344</v>
@@ -18611,68 +18604,68 @@
     </row>
     <row r="881" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A881" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B881" t="s">
         <v>1704</v>
       </c>
-      <c r="B881" t="s">
+      <c r="C881" s="5">
+        <v>1</v>
+      </c>
+      <c r="D881" t="s">
         <v>1705</v>
-      </c>
-      <c r="C881" s="5">
-        <v>1</v>
-      </c>
-      <c r="D881" t="s">
-        <v>1706</v>
       </c>
       <c r="E881" s="2"/>
     </row>
     <row r="882" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A882" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C882" s="5">
+        <v>1</v>
+      </c>
+      <c r="D882" t="s">
         <v>1707</v>
       </c>
-      <c r="C882" s="5">
-        <v>1</v>
-      </c>
-      <c r="D882" t="s">
+      <c r="E882" t="s">
         <v>1708</v>
-      </c>
-      <c r="E882" t="s">
-        <v>1709</v>
       </c>
     </row>
     <row r="883" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A883" s="2" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B883" s="2"/>
       <c r="C883" s="5">
         <v>1</v>
       </c>
       <c r="D883" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E883" t="s">
         <v>1711</v>
-      </c>
-      <c r="E883" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="884" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A884" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B884" t="s">
         <v>1713</v>
       </c>
-      <c r="B884" t="s">
+      <c r="C884" s="5">
+        <v>1</v>
+      </c>
+      <c r="D884" t="s">
         <v>1714</v>
       </c>
-      <c r="C884" s="5">
-        <v>1</v>
-      </c>
-      <c r="D884" t="s">
+      <c r="E884" t="s">
         <v>1715</v>
-      </c>
-      <c r="E884" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="885" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A885" s="2" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="B885" s="2"/>
       <c r="C885" s="5">
@@ -18680,61 +18673,61 @@
       </c>
       <c r="D885" s="2"/>
       <c r="E885" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="886" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A886" s="2" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="B886" s="2"/>
       <c r="C886" s="5">
         <v>1</v>
       </c>
       <c r="D886" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E886" t="s">
         <v>1720</v>
-      </c>
-      <c r="E886" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="887" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A887" s="2" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="B887" s="2"/>
       <c r="C887" s="5">
         <v>1</v>
       </c>
       <c r="D887" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="E887" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="888" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A888" s="2" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="C888" s="5">
         <v>1</v>
       </c>
       <c r="D888" s="2"/>
       <c r="E888" s="7" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="889" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A889" s="2" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B889" s="2"/>
       <c r="C889" s="5">
         <v>1</v>
       </c>
       <c r="D889" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="E889" t="s">
         <v>1215</v>
@@ -18742,22 +18735,22 @@
     </row>
     <row r="890" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A890" s="2" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B890" s="2"/>
       <c r="C890" s="5">
         <v>1</v>
       </c>
       <c r="D890" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="E890" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="891" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:3">
       <c r="A891" s="2" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B891" s="2"/>
       <c r="C891" s="5">
@@ -18766,7 +18759,7 @@
     </row>
     <row r="892" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A892" s="2" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B892" s="2"/>
       <c r="C892" s="5">
@@ -18776,12 +18769,12 @@
         <v>1064</v>
       </c>
       <c r="E892" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="893" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A893" s="2" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="B893" s="2"/>
       <c r="C893" s="5">
@@ -18791,12 +18784,12 @@
         <v>1370</v>
       </c>
       <c r="E893" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="894" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A894" s="2" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="B894" s="7" t="s">
         <v>1603</v>
@@ -18809,7 +18802,7 @@
     </row>
     <row r="895" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A895" s="2" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B895" s="2"/>
       <c r="C895" s="5">
@@ -18820,7 +18813,7 @@
     </row>
     <row r="896" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A896" s="2" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B896" s="2"/>
       <c r="C896" s="5">
@@ -18831,22 +18824,22 @@
     </row>
     <row r="897" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A897" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B897" t="s">
         <v>1738</v>
       </c>
-      <c r="B897" t="s">
+      <c r="C897" s="5">
+        <v>1</v>
+      </c>
+      <c r="D897" t="s">
         <v>1739</v>
-      </c>
-      <c r="C897" s="5">
-        <v>1</v>
-      </c>
-      <c r="D897" t="s">
-        <v>1740</v>
       </c>
       <c r="E897" s="2"/>
     </row>
     <row r="898" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A898" s="2" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B898" s="2"/>
       <c r="C898" s="5">
@@ -18856,12 +18849,12 @@
         <v>270</v>
       </c>
       <c r="E898" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="899" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A899" s="2" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B899" s="2"/>
       <c r="C899" s="5">
@@ -18872,23 +18865,23 @@
     </row>
     <row r="900" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A900" s="2" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B900" s="2"/>
       <c r="C900" s="5">
         <v>1</v>
       </c>
       <c r="D900" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="E900" s="2"/>
     </row>
     <row r="901" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A901" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B901" s="7" t="s">
         <v>1746</v>
-      </c>
-      <c r="B901" s="7" t="s">
-        <v>1747</v>
       </c>
       <c r="C901" s="5">
         <v>1</v>
@@ -18898,7 +18891,7 @@
     </row>
     <row r="902" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A902" s="2" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B902" s="2"/>
       <c r="C902" s="5">
@@ -18909,7 +18902,7 @@
     </row>
     <row r="903" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A903" s="2" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B903" s="2"/>
       <c r="C903" s="5">
@@ -18920,31 +18913,31 @@
     </row>
     <row r="904" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A904" s="2" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B904" s="2"/>
       <c r="C904" s="5">
         <v>1</v>
       </c>
       <c r="D904" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="905" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A905" s="2" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B905" s="2"/>
       <c r="C905" s="5">
         <v>1</v>
       </c>
       <c r="D905" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="906" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A906" s="2" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B906" s="2"/>
       <c r="C906" s="5">
@@ -18954,12 +18947,12 @@
         <v>560</v>
       </c>
       <c r="E906" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="907" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A907" s="2" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B907" s="2"/>
       <c r="C907" s="5">
@@ -18970,25 +18963,25 @@
     </row>
     <row r="908" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A908" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B908" t="s">
         <v>1757</v>
       </c>
-      <c r="B908" t="s">
+      <c r="C908" s="5">
+        <v>1</v>
+      </c>
+      <c r="D908" t="s">
         <v>1758</v>
-      </c>
-      <c r="C908" s="5">
-        <v>1</v>
-      </c>
-      <c r="D908" t="s">
-        <v>1759</v>
       </c>
       <c r="E908" s="2"/>
     </row>
     <row r="909" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A909" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B909" t="s">
         <v>1760</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1761</v>
       </c>
       <c r="C909" s="5">
         <v>1</v>
@@ -19000,65 +18993,65 @@
     </row>
     <row r="910" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A910" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B910" t="s">
         <v>1762</v>
       </c>
-      <c r="B910" t="s">
+      <c r="C910" s="5">
+        <v>1</v>
+      </c>
+      <c r="E910" s="13" t="s">
         <v>1763</v>
-      </c>
-      <c r="C910" s="5">
-        <v>1</v>
-      </c>
-      <c r="E910" s="13" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="911" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A911" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B911" t="s">
         <v>1765</v>
       </c>
-      <c r="B911" t="s">
-        <v>1766</v>
-      </c>
       <c r="C911" s="5">
         <v>1</v>
       </c>
       <c r="E911" s="13" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="912" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A912" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B912" t="s">
         <v>1767</v>
       </c>
-      <c r="B912" t="s">
+      <c r="C912" s="5">
+        <v>1</v>
+      </c>
+      <c r="D912" t="s">
         <v>1768</v>
-      </c>
-      <c r="C912" s="5">
-        <v>1</v>
-      </c>
-      <c r="D912" t="s">
-        <v>1769</v>
       </c>
       <c r="E912" s="2"/>
     </row>
     <row r="913" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A913" s="2" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B913" s="2"/>
       <c r="C913" s="5">
         <v>1</v>
       </c>
       <c r="D913" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E913" t="s">
         <v>1771</v>
-      </c>
-      <c r="E913" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="914" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A914" s="2" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="B914" s="2"/>
       <c r="C914" s="5">
@@ -19069,7 +19062,7 @@
     </row>
     <row r="915" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:3">
       <c r="A915" s="2" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B915" s="2"/>
       <c r="C915" s="5">
@@ -19078,7 +19071,7 @@
     </row>
     <row r="916" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A916" s="2" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B916" s="2"/>
       <c r="C916" s="5">
@@ -19089,7 +19082,7 @@
     </row>
     <row r="917" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A917" s="2" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B917" s="2"/>
       <c r="C917" s="5">
@@ -19100,7 +19093,7 @@
     </row>
     <row r="918" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A918" s="2" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B918" s="2"/>
       <c r="C918" s="5">
@@ -19111,7 +19104,7 @@
     </row>
     <row r="919" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A919" s="2" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B919" s="2"/>
       <c r="C919" s="5">
@@ -19119,101 +19112,101 @@
       </c>
       <c r="D919" s="2"/>
       <c r="E919" s="2" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="920" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A920" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B920" t="s">
         <v>1780</v>
       </c>
-      <c r="B920" t="s">
+      <c r="C920" s="5">
+        <v>1</v>
+      </c>
+      <c r="E920" t="s">
         <v>1781</v>
-      </c>
-      <c r="C920" s="5">
-        <v>1</v>
-      </c>
-      <c r="E920" t="s">
-        <v>1782</v>
       </c>
     </row>
     <row r="921" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A921" s="2" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B921" s="2"/>
       <c r="C921" s="5">
         <v>1</v>
       </c>
       <c r="D921" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E921" s="7" t="s">
         <v>1784</v>
-      </c>
-      <c r="E921" s="7" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="922" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A922" s="2" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B922" s="2"/>
       <c r="C922" s="5">
         <v>1</v>
       </c>
       <c r="D922" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E922" s="7" t="s">
         <v>1784</v>
-      </c>
-      <c r="E922" s="7" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="923" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A923" s="2" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B923" s="2"/>
       <c r="C923" s="5">
         <v>1</v>
       </c>
       <c r="D923" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E923" s="7" t="s">
         <v>1784</v>
-      </c>
-      <c r="E923" s="7" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="924" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A924" s="2" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B924" s="2"/>
       <c r="C924" s="5">
         <v>1</v>
       </c>
       <c r="D924" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E924" s="7" t="s">
         <v>1784</v>
-      </c>
-      <c r="E924" s="7" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="925" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A925" s="2" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B925" s="2"/>
       <c r="C925" s="5">
         <v>1</v>
       </c>
       <c r="D925" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E925" s="7" t="s">
         <v>1784</v>
-      </c>
-      <c r="E925" s="7" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="926" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A926" s="2" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B926" s="2"/>
       <c r="C926" s="5">
@@ -19221,27 +19214,27 @@
       </c>
       <c r="D926" s="2"/>
       <c r="E926" s="12" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="927" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A927" s="2" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B927" s="2"/>
       <c r="C927" s="5">
         <v>1</v>
       </c>
       <c r="D927" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="E927" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="928" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A928" s="2" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B928" t="s">
         <v>1418</v>
@@ -19254,7 +19247,7 @@
     </row>
     <row r="929" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A929" s="2" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="B929" t="s">
         <v>1416</v>
@@ -19267,7 +19260,7 @@
     </row>
     <row r="930" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A930" s="2" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B930" t="s">
         <v>1420</v>
@@ -19280,7 +19273,7 @@
     </row>
     <row r="931" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A931" s="2" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="B931" s="2"/>
       <c r="C931" s="5">
@@ -19291,7 +19284,7 @@
     </row>
     <row r="932" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A932" s="2" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="B932" s="2"/>
       <c r="C932" s="5">
@@ -19302,7 +19295,7 @@
     </row>
     <row r="933" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A933" s="2" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="B933" s="2"/>
       <c r="C933" s="5">
@@ -19313,7 +19306,7 @@
     </row>
     <row r="934" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A934" s="2" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="B934" s="2"/>
       <c r="C934" s="5">
@@ -19324,7 +19317,7 @@
     </row>
     <row r="935" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A935" s="2" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="B935" s="2"/>
       <c r="C935" s="5">
@@ -19335,7 +19328,7 @@
     </row>
     <row r="936" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A936" s="2" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B936" s="2"/>
       <c r="C936" s="5">
@@ -19346,7 +19339,7 @@
     </row>
     <row r="937" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A937" s="2" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B937" s="2"/>
       <c r="C937" s="5">
@@ -19357,7 +19350,7 @@
     </row>
     <row r="938" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A938" s="2" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B938" s="2"/>
       <c r="C938" s="5">
@@ -19368,7 +19361,7 @@
     </row>
     <row r="939" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A939" s="2" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B939" s="2"/>
       <c r="C939" s="5">
@@ -19380,7 +19373,7 @@
     </row>
     <row r="940" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A940" s="2" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B940" s="2"/>
       <c r="C940" s="5">
@@ -19391,7 +19384,7 @@
     </row>
     <row r="941" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A941" s="2" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B941" s="2"/>
       <c r="C941" s="5">
@@ -19402,7 +19395,7 @@
     </row>
     <row r="942" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A942" s="2" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="B942" s="2"/>
       <c r="C942" s="5">
@@ -19414,34 +19407,34 @@
     </row>
     <row r="943" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A943" s="2" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B943" s="2"/>
       <c r="C943" s="5">
         <v>1</v>
       </c>
       <c r="D943" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="944" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A944" s="2" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B944" s="2"/>
       <c r="C944" s="5">
         <v>1</v>
       </c>
       <c r="D944" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="945" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:3">
       <c r="A945" s="2" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="B945" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="C945" s="5">
         <v>1</v>
@@ -19449,7 +19442,7 @@
     </row>
     <row r="946" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A946" s="2" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B946" s="2"/>
       <c r="C946" s="5">
@@ -19460,7 +19453,7 @@
     </row>
     <row r="947" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A947" s="2" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="B947" s="2"/>
       <c r="C947" s="5">
@@ -19471,7 +19464,7 @@
     </row>
     <row r="948" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A948" s="2" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="B948" s="2"/>
       <c r="C948" s="5">
@@ -19482,7 +19475,7 @@
     </row>
     <row r="949" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A949" s="2" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="B949" s="2"/>
       <c r="C949" s="5">
@@ -19493,52 +19486,52 @@
     </row>
     <row r="950" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A950" s="2" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B950" s="2"/>
       <c r="C950" s="5">
         <v>1</v>
       </c>
       <c r="D950" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E950" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="951" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A951" s="2" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B951" s="2"/>
       <c r="C951" s="5">
         <v>1</v>
       </c>
       <c r="D951" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E951" t="s">
         <v>1819</v>
-      </c>
-      <c r="E951" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="952" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A952" s="2" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B952" s="2"/>
       <c r="C952" s="5">
         <v>1</v>
       </c>
       <c r="D952" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E952" t="s">
         <v>1819</v>
-      </c>
-      <c r="E952" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="953" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A953" s="2" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="B953" s="2"/>
       <c r="C953" s="5">
@@ -19549,37 +19542,37 @@
     </row>
     <row r="954" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A954" s="2" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B954" s="2"/>
       <c r="C954" s="5">
         <v>1</v>
       </c>
       <c r="D954" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E954" t="s">
         <v>1824</v>
-      </c>
-      <c r="E954" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="955" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A955" s="2" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B955" s="2"/>
       <c r="C955" s="5">
         <v>1</v>
       </c>
       <c r="D955" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E955" t="s">
         <v>1824</v>
-      </c>
-      <c r="E955" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="956" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A956" s="2" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="B956" t="s">
         <v>109</v>
@@ -19589,12 +19582,12 @@
       </c>
       <c r="D956" s="2"/>
       <c r="E956" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="957" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A957" s="2" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B957" s="2"/>
       <c r="C957" s="5">
@@ -19606,7 +19599,7 @@
     </row>
     <row r="958" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A958" s="2" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="B958" s="2"/>
       <c r="C958" s="5">
@@ -19617,7 +19610,7 @@
     </row>
     <row r="959" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A959" s="2" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B959" s="2"/>
       <c r="C959" s="5">
@@ -19628,7 +19621,7 @@
     </row>
     <row r="960" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A960" s="2" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B960" s="2"/>
       <c r="C960" s="5">
@@ -19640,7 +19633,7 @@
     </row>
     <row r="961" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A961" s="2" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B961" s="2"/>
       <c r="C961" s="5">
@@ -19652,39 +19645,39 @@
     </row>
     <row r="962" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A962" s="2" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="B962" s="2"/>
       <c r="C962" s="5">
         <v>1</v>
       </c>
       <c r="D962" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E962" t="s">
         <v>1835</v>
-      </c>
-      <c r="E962" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="963" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A963" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C963" s="5">
+        <v>1</v>
+      </c>
+      <c r="D963" t="s">
         <v>1837</v>
       </c>
-      <c r="C963" s="5">
-        <v>1</v>
-      </c>
-      <c r="D963" t="s">
+      <c r="E963" s="2" t="s">
         <v>1838</v>
-      </c>
-      <c r="E963" s="2" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="964" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A964" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B964" t="s">
         <v>1840</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1841</v>
       </c>
       <c r="C964" s="5">
         <v>1</v>
@@ -19694,10 +19687,10 @@
     </row>
     <row r="965" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A965" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B965" t="s">
         <v>1842</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1843</v>
       </c>
       <c r="C965" s="5">
         <v>1</v>
@@ -19707,34 +19700,34 @@
     </row>
     <row r="966" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A966" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B966" t="s">
         <v>1844</v>
       </c>
-      <c r="B966" t="s">
+      <c r="C966" s="5">
+        <v>1</v>
+      </c>
+      <c r="D966" t="s">
         <v>1845</v>
-      </c>
-      <c r="C966" s="5">
-        <v>1</v>
-      </c>
-      <c r="D966" t="s">
-        <v>1846</v>
       </c>
       <c r="E966" s="2"/>
     </row>
     <row r="967" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A967" s="2" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B967" s="2"/>
       <c r="C967" s="5">
         <v>1</v>
       </c>
       <c r="E967" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="968" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A968" s="2" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="B968" s="2"/>
       <c r="C968" s="5">
@@ -19745,7 +19738,7 @@
     </row>
     <row r="969" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A969" s="2" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B969" s="2"/>
       <c r="C969" s="5">
@@ -19757,37 +19750,37 @@
     </row>
     <row r="970" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A970" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B970" t="s">
         <v>1851</v>
       </c>
-      <c r="B970" t="s">
+      <c r="C970" s="5">
+        <v>1</v>
+      </c>
+      <c r="D970" t="s">
         <v>1852</v>
-      </c>
-      <c r="C970" s="5">
-        <v>1</v>
-      </c>
-      <c r="D970" t="s">
-        <v>1853</v>
       </c>
       <c r="E970" s="2"/>
     </row>
     <row r="971" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A971" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B971" t="s">
         <v>1854</v>
       </c>
-      <c r="B971" t="s">
+      <c r="C971" s="5">
+        <v>1</v>
+      </c>
+      <c r="D971" t="s">
         <v>1855</v>
-      </c>
-      <c r="C971" s="5">
-        <v>1</v>
-      </c>
-      <c r="D971" t="s">
-        <v>1856</v>
       </c>
       <c r="E971" s="2"/>
     </row>
     <row r="972" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A972" s="2" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="C972" s="5">
         <v>1</v>
@@ -19797,7 +19790,7 @@
     </row>
     <row r="973" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A973" s="2" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="B973" s="2"/>
       <c r="C973" s="5">
@@ -19809,19 +19802,19 @@
     </row>
     <row r="974" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A974" s="2" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="B974" s="2"/>
       <c r="C974" s="5">
         <v>1</v>
       </c>
       <c r="D974" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="975" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:3">
       <c r="A975" s="2" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B975" s="2"/>
       <c r="C975" s="5">
@@ -19830,10 +19823,10 @@
     </row>
     <row r="976" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A976" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B976" t="s">
         <v>1862</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1863</v>
       </c>
       <c r="C976" s="5">
         <v>1</v>
@@ -19843,19 +19836,19 @@
     </row>
     <row r="977" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A977" s="2" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="B977" s="2"/>
       <c r="C977" s="5">
         <v>1</v>
       </c>
       <c r="D977" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="978" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A978" s="2" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="B978" s="2"/>
       <c r="C978" s="5">
@@ -19866,7 +19859,7 @@
     </row>
     <row r="979" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A979" s="2" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="B979" s="2"/>
       <c r="C979" s="5">
@@ -19877,7 +19870,7 @@
     </row>
     <row r="980" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A980" s="2" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="B980" s="2"/>
       <c r="C980" s="5">
@@ -19888,7 +19881,7 @@
     </row>
     <row r="981" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A981" s="2" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B981" s="2"/>
       <c r="C981" s="5">
@@ -19899,46 +19892,46 @@
     </row>
     <row r="982" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A982" s="2" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="B982" s="2"/>
       <c r="C982" s="5">
         <v>1</v>
       </c>
       <c r="D982" s="7" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E982" s="2"/>
     </row>
     <row r="983" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A983" s="2" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B983" s="2"/>
       <c r="C983" s="5">
         <v>1</v>
       </c>
       <c r="D983" s="7" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E983" s="2"/>
     </row>
     <row r="984" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A984" s="2" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B984" s="2"/>
       <c r="C984" s="5">
         <v>1</v>
       </c>
       <c r="D984" s="7" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E984" s="2"/>
     </row>
     <row r="985" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A985" s="2" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B985" s="2"/>
       <c r="C985" s="5">
@@ -19949,7 +19942,7 @@
     </row>
     <row r="986" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A986" s="2" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="B986" s="2"/>
       <c r="C986" s="5">
@@ -19962,20 +19955,20 @@
     </row>
     <row r="987" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A987" s="2" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B987" s="2"/>
       <c r="C987" s="5">
         <v>1</v>
       </c>
       <c r="D987" s="2" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="E987" s="2"/>
     </row>
     <row r="988" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A988" s="2" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B988" s="2"/>
       <c r="C988" s="5">
@@ -19986,10 +19979,10 @@
     </row>
     <row r="989" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A989" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B989" s="7" t="s">
         <v>1878</v>
-      </c>
-      <c r="B989" s="7" t="s">
-        <v>1879</v>
       </c>
       <c r="C989" s="5">
         <v>1</v>
@@ -19999,7 +19992,7 @@
     </row>
     <row r="990" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A990" s="2" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="B990" s="2"/>
       <c r="C990" s="5">
@@ -20010,7 +20003,7 @@
     </row>
     <row r="991" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A991" s="2" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="B991" s="2"/>
       <c r="C991" s="5">
@@ -20021,10 +20014,10 @@
     </row>
     <row r="992" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A992" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B992" s="2" t="s">
         <v>1882</v>
-      </c>
-      <c r="B992" s="2" t="s">
-        <v>1883</v>
       </c>
       <c r="C992" s="5">
         <v>1</v>
@@ -20034,7 +20027,7 @@
     </row>
     <row r="993" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A993" s="2" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B993" s="2"/>
       <c r="C993" s="5">
@@ -20045,10 +20038,10 @@
     </row>
     <row r="994" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A994" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B994" t="s">
         <v>1885</v>
-      </c>
-      <c r="B994" t="s">
-        <v>1886</v>
       </c>
       <c r="C994" s="5">
         <v>1</v>
@@ -20058,7 +20051,7 @@
     </row>
     <row r="995" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A995" s="2" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B995" s="2"/>
       <c r="C995" s="5">
@@ -20068,43 +20061,43 @@
         <v>1652</v>
       </c>
       <c r="E995" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="996" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A996" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B996" s="2"/>
       <c r="C996" s="5">
         <v>1</v>
       </c>
       <c r="D996" s="7" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="E996" s="2"/>
     </row>
     <row r="997" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A997" s="2" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B997" s="2"/>
       <c r="C997" s="5">
         <v>1</v>
       </c>
       <c r="D997" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E997" t="s">
         <v>1892</v>
-      </c>
-      <c r="E997" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="998" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A998" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B998" s="2" t="s">
         <v>1894</v>
-      </c>
-      <c r="B998" s="2" t="s">
-        <v>1895</v>
       </c>
       <c r="C998" s="5">
         <v>1</v>
@@ -20114,7 +20107,7 @@
     </row>
     <row r="999" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A999" s="2" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B999" s="2"/>
       <c r="C999" s="5">
@@ -20125,58 +20118,58 @@
     </row>
     <row r="1000" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1000" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C1000" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E1000" t="s">
         <v>1897</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1714</v>
-      </c>
-      <c r="C1000" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1000" t="s">
-        <v>1715</v>
-      </c>
-      <c r="E1000" t="s">
-        <v>1898</v>
       </c>
     </row>
     <row r="1001" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1001" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C1001" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E1001" t="s">
         <v>1899</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1714</v>
-      </c>
-      <c r="C1001" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1001" t="s">
-        <v>1715</v>
-      </c>
-      <c r="E1001" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="1002" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1002" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C1002" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E1002" t="s">
         <v>1901</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1714</v>
-      </c>
-      <c r="C1002" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1002" t="s">
-        <v>1715</v>
-      </c>
-      <c r="E1002" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="1003" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1003" s="2" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B1003" s="2"/>
       <c r="C1003" s="5">
@@ -20186,25 +20179,25 @@
         <v>1652</v>
       </c>
       <c r="E1003" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1004" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1004" s="2" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B1004" s="2"/>
       <c r="C1004" s="5">
         <v>1</v>
       </c>
       <c r="D1004" s="7" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="E1004" s="2"/>
     </row>
     <row r="1005" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1005" s="2" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B1005" s="7" t="s">
         <v>1560</v>
@@ -20217,7 +20210,7 @@
     </row>
     <row r="1006" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1006" s="2" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B1006" s="2"/>
       <c r="C1006" s="5">
@@ -20228,7 +20221,7 @@
     </row>
     <row r="1007" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1007" s="2" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B1007" s="2"/>
       <c r="C1007" s="5">
@@ -20239,7 +20232,7 @@
     </row>
     <row r="1008" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1008" s="2" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B1008" s="2"/>
       <c r="C1008" s="5">
@@ -20250,60 +20243,60 @@
     </row>
     <row r="1009" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1009" s="2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B1009" s="2"/>
       <c r="C1009" s="5">
         <v>1</v>
       </c>
       <c r="D1009" s="7" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="E1009" s="2"/>
     </row>
     <row r="1010" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1010" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C1010" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1010" t="s">
         <v>1913</v>
       </c>
-      <c r="C1010" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1010" t="s">
+      <c r="E1010" t="s">
         <v>1914</v>
-      </c>
-      <c r="E1010" t="s">
-        <v>1915</v>
       </c>
     </row>
     <row r="1011" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1011" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C1011" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1011" t="s">
         <v>1916</v>
       </c>
-      <c r="C1011" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1011" t="s">
-        <v>1917</v>
-      </c>
       <c r="E1011" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1012" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A1012" s="2" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B1012" s="2"/>
       <c r="C1012" s="5">
         <v>1</v>
       </c>
       <c r="D1012" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1013" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A1013" s="2" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B1013" s="2"/>
       <c r="C1013" s="5">
@@ -20315,7 +20308,7 @@
     </row>
     <row r="1014" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1014" s="2" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B1014" s="2"/>
       <c r="C1014" s="5">
@@ -20326,7 +20319,7 @@
     </row>
     <row r="1015" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1015" s="2" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B1015" s="2"/>
       <c r="C1015" s="5">
@@ -20339,56 +20332,56 @@
     </row>
     <row r="1016" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A1016" s="2" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B1016" s="2"/>
       <c r="C1016" s="5">
         <v>1</v>
       </c>
       <c r="D1016" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1017" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1017" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C1017" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1017" s="7" t="s">
         <v>1925</v>
-      </c>
-      <c r="C1017" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1017" s="7" t="s">
-        <v>1926</v>
       </c>
       <c r="E1017" s="2"/>
     </row>
     <row r="1018" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1018" s="2" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B1018" s="2"/>
       <c r="C1018" s="5">
         <v>1</v>
       </c>
       <c r="D1018" s="7" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E1018" s="2"/>
     </row>
     <row r="1019" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:4">
       <c r="A1019" s="2" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B1019" s="2"/>
       <c r="C1019" s="5">
         <v>1</v>
       </c>
       <c r="D1019" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1020" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1020" s="2" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B1020" s="2"/>
       <c r="C1020" s="5">
@@ -20401,7 +20394,7 @@
     </row>
     <row r="1021" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1021" s="2" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B1021" s="2"/>
       <c r="C1021" s="5">
@@ -20409,12 +20402,12 @@
       </c>
       <c r="D1021" s="2"/>
       <c r="E1021" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1022" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1022" s="2" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B1022" s="2"/>
       <c r="C1022" s="5">
@@ -20422,12 +20415,12 @@
       </c>
       <c r="D1022" s="2"/>
       <c r="E1022" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1023" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1023" s="2" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="B1023" s="2"/>
       <c r="C1023" s="5">
@@ -20435,95 +20428,95 @@
       </c>
       <c r="D1023" s="2"/>
       <c r="E1023" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1024" s="1" customFormat="1" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1024" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C1024" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E1024" t="s">
         <v>1936</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>1714</v>
-      </c>
-      <c r="C1024" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1024" t="s">
-        <v>1715</v>
-      </c>
-      <c r="E1024" t="s">
-        <v>1937</v>
       </c>
     </row>
     <row r="1025" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1025" s="2" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="C1025" s="5">
         <v>1</v>
       </c>
       <c r="E1025" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1026" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1026" s="2" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C1026" s="5">
         <v>1</v>
       </c>
       <c r="E1026" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1027" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1027" s="2" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C1027" s="5">
         <v>1</v>
       </c>
       <c r="E1027" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1028" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1028" s="2" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="C1028" s="5">
         <v>1</v>
       </c>
       <c r="E1028" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1029" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1029" s="2" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="C1029" s="5">
         <v>1</v>
       </c>
       <c r="E1029" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1030" ht="16.8" customHeight="1" spans="1:5">
       <c r="A1030" s="2" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C1030" s="5">
         <v>1</v>
       </c>
       <c r="E1030" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1031" ht="16.8" spans="1:4">
       <c r="A1031" s="2" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="C1031" s="5">
         <v>1</v>
@@ -20532,10 +20525,10 @@
     </row>
     <row r="1032" ht="16.8" spans="1:3">
       <c r="A1032" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1032" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>1946</v>
       </c>
       <c r="C1032" s="5">
         <v>1</v>
@@ -20543,10 +20536,10 @@
     </row>
     <row r="1033" ht="16.8" spans="1:4">
       <c r="A1033" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1033" t="s">
         <v>1947</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>1948</v>
       </c>
       <c r="C1033" s="5">
         <v>1</v>
@@ -20555,21 +20548,21 @@
     </row>
     <row r="1034" ht="16.8" spans="1:4">
       <c r="A1034" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C1034" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1034" t="s">
         <v>1949</v>
-      </c>
-      <c r="C1034" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1034" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="1035" ht="16.8" spans="1:3">
       <c r="A1035" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1035" t="s">
         <v>1951</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>1952</v>
       </c>
       <c r="C1035" s="5">
         <v>1</v>
@@ -20577,10 +20570,10 @@
     </row>
     <row r="1036" ht="16.8" spans="1:3">
       <c r="A1036" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1036" t="s">
         <v>1953</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>1954</v>
       </c>
       <c r="C1036" s="5">
         <v>1</v>
@@ -20588,10 +20581,10 @@
     </row>
     <row r="1037" ht="16.8" spans="1:3">
       <c r="A1037" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B1037" t="s">
         <v>1955</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>1956</v>
       </c>
       <c r="C1037" s="5">
         <v>1</v>
@@ -20599,7 +20592,7 @@
     </row>
     <row r="1038" ht="16.8" spans="1:4">
       <c r="A1038" s="2" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C1038" s="5">
         <v>1</v>
@@ -20608,7 +20601,7 @@
     </row>
     <row r="1039" ht="16.8" spans="1:4">
       <c r="A1039" s="2" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C1039" s="5">
         <v>1</v>
@@ -20617,7 +20610,7 @@
     </row>
     <row r="1040" ht="16.8" spans="1:4">
       <c r="A1040" s="2" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C1040" s="5">
         <v>1</v>
@@ -20626,10 +20619,10 @@
     </row>
     <row r="1041" ht="16" spans="1:3">
       <c r="A1041" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B1041" s="14" t="s">
         <v>1960</v>
-      </c>
-      <c r="B1041" s="14" t="s">
-        <v>1961</v>
       </c>
       <c r="C1041" s="5">
         <v>1</v>
@@ -20637,7 +20630,7 @@
     </row>
     <row r="1042" ht="16.8" spans="1:4">
       <c r="A1042" s="2" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C1042" s="5">
         <v>1</v>
@@ -20648,7 +20641,7 @@
     </row>
     <row r="1043" ht="16.8" spans="1:4">
       <c r="A1043" s="2" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C1043" s="5">
         <v>1</v>
@@ -20659,7 +20652,7 @@
     </row>
     <row r="1044" ht="16.8" spans="1:4">
       <c r="A1044" s="2" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C1044" s="5">
         <v>1</v>
@@ -20668,7 +20661,7 @@
     </row>
     <row r="1045" ht="16.8" spans="1:4">
       <c r="A1045" s="2" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C1045" s="5">
         <v>1</v>
@@ -20679,7 +20672,7 @@
     </row>
     <row r="1046" ht="16.8" spans="1:4">
       <c r="A1046" s="2" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C1046" s="5">
         <v>1</v>
@@ -20690,7 +20683,7 @@
     </row>
     <row r="1047" ht="16.8" spans="1:4">
       <c r="A1047" s="2" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="C1047" s="5">
         <v>1</v>
@@ -20701,10 +20694,10 @@
     </row>
     <row r="1048" ht="16.8" spans="1:4">
       <c r="A1048" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B1048" s="14" t="s">
         <v>1968</v>
-      </c>
-      <c r="B1048" s="14" t="s">
-        <v>1969</v>
       </c>
       <c r="C1048" s="5">
         <v>1</v>
@@ -20713,32 +20706,32 @@
     </row>
     <row r="1049" ht="16.8" spans="1:4">
       <c r="A1049" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C1049" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1049" t="s">
         <v>1970</v>
-      </c>
-      <c r="C1049" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1049" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="1050" ht="16.8" spans="1:5">
       <c r="A1050" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1050" t="s">
         <v>1972</v>
       </c>
-      <c r="B1050" t="s">
+      <c r="C1050" s="5">
+        <v>1</v>
+      </c>
+      <c r="E1050" s="2" t="s">
         <v>1973</v>
-      </c>
-      <c r="C1050" s="5">
-        <v>1</v>
-      </c>
-      <c r="E1050" s="2" t="s">
-        <v>1974</v>
       </c>
     </row>
     <row r="1051" ht="16.8" spans="1:4">
       <c r="A1051" s="2" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C1051" s="5">
         <v>1</v>
@@ -20747,7 +20740,7 @@
     </row>
     <row r="1052" ht="16.8" spans="1:4">
       <c r="A1052" s="2" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C1052" s="5">
         <v>1</v>
@@ -20756,7 +20749,7 @@
     </row>
     <row r="1053" ht="16.8" spans="1:4">
       <c r="A1053" s="2" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C1053" s="5">
         <v>1</v>
@@ -20765,7 +20758,7 @@
     </row>
     <row r="1054" ht="16.8" spans="1:4">
       <c r="A1054" s="2" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="C1054" s="5">
         <v>1</v>
@@ -20774,7 +20767,7 @@
     </row>
     <row r="1055" ht="16.8" spans="1:4">
       <c r="A1055" s="2" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="C1055" s="5">
         <v>1</v>
@@ -20783,19 +20776,19 @@
     </row>
     <row r="1056" ht="16.8" spans="1:5">
       <c r="A1056" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1980</v>
       </c>
-      <c r="B1056" t="s">
+      <c r="C1056" s="5">
+        <v>1</v>
+      </c>
+      <c r="D1056" t="s">
         <v>1981</v>
       </c>
-      <c r="C1056" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1056" t="s">
+      <c r="E1056" s="2" t="s">
         <v>1982</v>
-      </c>
-      <c r="E1056" s="2" t="s">
-        <v>1983</v>
       </c>
     </row>
   </sheetData>
